--- a/data/trans_dic/P16A06-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A06-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,82</t>
+          <t>0,36; 4,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,1</t>
+          <t>0,93; 4,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,84</t>
+          <t>0,9; 5,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,39</t>
+          <t>1,9; 5,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,1</t>
+          <t>1,05; 5,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,09</t>
+          <t>3,4; 9,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 12,78</t>
+          <t>5,57; 13,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,07</t>
+          <t>4,83; 9,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,84</t>
+          <t>1,02; 3,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,03</t>
+          <t>2,43; 5,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,0</t>
+          <t>3,93; 7,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,55</t>
+          <t>3,82; 6,64</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,73</t>
+          <t>0,58; 2,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,8</t>
+          <t>1,19; 5,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,23</t>
+          <t>1,43; 4,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,57</t>
+          <t>3,18; 7,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,18</t>
+          <t>3,8; 7,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,35</t>
+          <t>5,56; 10,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,83</t>
+          <t>4,9; 9,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,6</t>
+          <t>8,96; 13,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,89</t>
+          <t>2,7; 4,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,99</t>
+          <t>3,66; 6,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 6,39</t>
+          <t>3,69; 6,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 9,91</t>
+          <t>6,66; 9,72</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,45</t>
+          <t>0,6; 3,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,68</t>
+          <t>3,94; 8,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,45</t>
+          <t>0,27; 2,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,4</t>
+          <t>1,17; 4,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,26</t>
+          <t>2,71; 7,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,81</t>
+          <t>8,47; 13,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,5</t>
+          <t>0,15; 1,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,47</t>
+          <t>1,08; 3,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,17</t>
+          <t>1,65; 4,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 10,82</t>
+          <t>6,87; 10,24</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,13</t>
+          <t>0,28; 3,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,85</t>
+          <t>0,81; 3,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,4</t>
+          <t>1,22; 4,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 9,72</t>
+          <t>3,72; 9,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,17</t>
+          <t>1,58; 5,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 10,37</t>
+          <t>5,08; 10,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 12,64</t>
+          <t>6,81; 12,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,5</t>
+          <t>4,3; 10,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,49</t>
+          <t>1,22; 3,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,44</t>
+          <t>3,39; 6,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,11</t>
+          <t>4,31; 7,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,3</t>
+          <t>4,81; 9,21</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,86</t>
+          <t>0,85; 4,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,92</t>
+          <t>0,93; 5,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,49</t>
+          <t>1,38; 7,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,2</t>
+          <t>2,0; 6,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 9,51</t>
+          <t>3,01; 9,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,67; 23,56</t>
+          <t>12,77; 23,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 13,2</t>
+          <t>5,25; 13,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,44; 13,84</t>
+          <t>8,49; 13,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,92</t>
+          <t>2,22; 6,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 13,3</t>
+          <t>7,26; 13,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,93</t>
+          <t>4,12; 9,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,51</t>
+          <t>5,9; 9,44</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,21</t>
+          <t>0,35; 2,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,67</t>
+          <t>2,05; 6,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,81; 12,13</t>
+          <t>6,8; 12,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,91</t>
+          <t>1,09; 5,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,86</t>
+          <t>1,75; 6,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 15,37</t>
+          <t>7,68; 15,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,57; 19,75</t>
+          <t>13,43; 20,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,27</t>
+          <t>0,89; 3,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,99</t>
+          <t>1,12; 3,79</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,34; 9,82</t>
+          <t>5,36; 10,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,84; 14,96</t>
+          <t>10,66; 14,89</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,6</t>
+          <t>1,18; 3,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,48</t>
+          <t>0,46; 2,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,07</t>
+          <t>3,51; 7,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,26</t>
+          <t>3,73; 7,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,57</t>
+          <t>2,44; 5,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,11</t>
+          <t>1,63; 4,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 10,9</t>
+          <t>6,37; 10,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 13,42</t>
+          <t>4,62; 13,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,0</t>
+          <t>2,06; 4,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,9</t>
+          <t>1,25; 2,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,48</t>
+          <t>5,41; 8,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,68</t>
+          <t>5,11; 9,84</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,44</t>
+          <t>2,7; 5,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,62</t>
+          <t>2,01; 4,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,26</t>
+          <t>0,49; 2,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,55</t>
+          <t>1,26; 4,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,11</t>
+          <t>4,53; 8,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,95; 9,72</t>
+          <t>5,86; 9,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,33</t>
+          <t>3,99; 7,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,58</t>
+          <t>7,23; 11,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,01; 6,18</t>
+          <t>4,06; 6,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,67</t>
+          <t>4,3; 6,68</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,41</t>
+          <t>2,48; 4,41</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,01</t>
+          <t>3,24; 7,0</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,47</t>
+          <t>1,53; 2,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,63</t>
+          <t>1,59; 2,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,31</t>
+          <t>2,1; 3,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,7</t>
+          <t>3,75; 5,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,86</t>
+          <t>3,5; 4,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,17</t>
+          <t>5,55; 7,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,62; 8,4</t>
+          <t>6,62; 8,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,32; 10,99</t>
+          <t>7,96; 10,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,54</t>
+          <t>2,65; 3,51</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,68</t>
+          <t>3,79; 4,76</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,75</t>
+          <t>4,62; 5,72</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,13</t>
+          <t>6,46; 8,16</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>879; 10427</t>
+          <t>982; 11790</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2507; 14836</t>
+          <t>2711; 14182</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2610; 14219</t>
+          <t>2641; 15145</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5520; 16788</t>
+          <t>5903; 18360</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2179; 13313</t>
+          <t>2741; 14565</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9289; 25386</t>
+          <t>9505; 25784</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16981; 36911</t>
+          <t>16082; 37547</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13870; 26279</t>
+          <t>14001; 26088</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5345; 20474</t>
+          <t>5451; 18876</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14889; 34376</t>
+          <t>13845; 32823</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21664; 46573</t>
+          <t>22866; 46546</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22946; 39366</t>
+          <t>22965; 39920</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2945; 13484</t>
+          <t>2870; 13834</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5061; 24271</t>
+          <t>6005; 25329</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7016; 21250</t>
+          <t>7203; 22654</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16615; 39190</t>
+          <t>16478; 37781</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20341; 41211</t>
+          <t>19151; 39817</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28472; 54099</t>
+          <t>29072; 55077</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25183; 51406</t>
+          <t>25637; 49754</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46169; 69861</t>
+          <t>46046; 69955</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25544; 48715</t>
+          <t>26930; 48299</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39873; 71884</t>
+          <t>37662; 68779</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37333; 65550</t>
+          <t>37796; 66175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69261; 102144</t>
+          <t>68646; 100201</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4732</t>
+          <t>0; 5225</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1946; 11143</t>
+          <t>1931; 10789</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7707</t>
+          <t>0; 8146</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12575; 27389</t>
+          <t>12424; 27365</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>907; 8224</t>
+          <t>911; 8441</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3204; 15006</t>
+          <t>3984; 15148</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8965; 24401</t>
+          <t>9098; 24482</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29363; 48216</t>
+          <t>29562; 47790</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>977; 9792</t>
+          <t>974; 9615</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7064; 23054</t>
+          <t>7150; 21986</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10537; 27285</t>
+          <t>10806; 27466</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46465; 71898</t>
+          <t>45658; 68059</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1635; 11226</t>
+          <t>1003; 11111</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3017; 14395</t>
+          <t>3042; 13206</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4262; 16280</t>
+          <t>4504; 15743</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11715; 30393</t>
+          <t>11615; 29749</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5489; 19211</t>
+          <t>5880; 20183</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19790; 40234</t>
+          <t>19712; 40300</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26014; 48971</t>
+          <t>26361; 49877</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20348; 49913</t>
+          <t>20465; 49517</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9164; 25455</t>
+          <t>8880; 25668</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26621; 49090</t>
+          <t>25820; 49404</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33349; 61384</t>
+          <t>32646; 60203</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38769; 73275</t>
+          <t>37922; 72602</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1737; 9881</t>
+          <t>1722; 9801</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1996; 12592</t>
+          <t>1973; 11595</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3720; 15820</t>
+          <t>2915; 15918</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3629; 11089</t>
+          <t>3577; 11026</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5951; 19745</t>
+          <t>6251; 19737</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27833; 51741</t>
+          <t>28040; 51390</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12161; 28847</t>
+          <t>11480; 28821</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17612; 28878</t>
+          <t>17719; 28814</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9575; 24324</t>
+          <t>9116; 24777</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31826; 57484</t>
+          <t>31363; 56867</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18314; 38379</t>
+          <t>17702; 39441</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23115; 36856</t>
+          <t>22862; 36589</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>955; 8705</t>
+          <t>953; 7898</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6110</t>
+          <t>0; 6276</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5596; 17548</t>
+          <t>5389; 16977</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18351; 32700</t>
+          <t>18335; 33212</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3014; 13661</t>
+          <t>3027; 14316</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4810; 19157</t>
+          <t>4886; 18484</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20240; 41977</t>
+          <t>20964; 42664</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34872; 50781</t>
+          <t>34519; 51801</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4872; 17952</t>
+          <t>4870; 17879</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6146; 22060</t>
+          <t>6170; 20963</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28637; 52670</t>
+          <t>28744; 54852</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>57089; 78773</t>
+          <t>56147; 78418</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7225; 22153</t>
+          <t>7259; 20909</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3896; 16379</t>
+          <t>3064; 16262</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21706; 46400</t>
+          <t>23028; 45995</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24424; 51542</t>
+          <t>23295; 49157</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15719; 35571</t>
+          <t>15544; 34586</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10296; 28539</t>
+          <t>11333; 29425</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43060; 75318</t>
+          <t>44022; 74661</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31779; 113896</t>
+          <t>39211; 113283</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26166; 50131</t>
+          <t>25813; 50553</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17606; 39328</t>
+          <t>16940; 39689</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73784; 114326</t>
+          <t>72922; 110214</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>74538; 142619</t>
+          <t>75264; 144968</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18379; 40423</t>
+          <t>20061; 40818</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15005; 35818</t>
+          <t>15616; 37633</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3926; 17600</t>
+          <t>3836; 16056</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11135; 42277</t>
+          <t>11698; 42398</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36487; 63518</t>
+          <t>35489; 63909</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>48873; 79857</t>
+          <t>48119; 81532</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31816; 60538</t>
+          <t>32999; 62144</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>51324; 82791</t>
+          <t>51710; 82357</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>61241; 94346</t>
+          <t>62016; 96306</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>68498; 106515</t>
+          <t>68625; 106696</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>39377; 70827</t>
+          <t>39766; 70804</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>53032; 115262</t>
+          <t>53307; 115117</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>50520; 80965</t>
+          <t>50187; 82874</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>52781; 90023</t>
+          <t>54220; 88623</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>73728; 112248</t>
+          <t>71362; 109099</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>131136; 196992</t>
+          <t>129731; 193911</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>116772; 164191</t>
+          <t>118361; 165057</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>192835; 254178</t>
+          <t>196652; 251511</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>234670; 297806</t>
+          <t>234505; 301382</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>304452; 401918</t>
+          <t>291033; 399005</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>180172; 235616</t>
+          <t>176275; 233535</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>258055; 326046</t>
+          <t>263880; 331559</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>318409; 399037</t>
+          <t>320372; 396633</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>455011; 578475</t>
+          <t>459592; 580537</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A06-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A06-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,32</t>
+          <t>0,32; 3,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,87</t>
+          <t>0,92; 4,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,16</t>
+          <t>0,95; 5,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,9</t>
+          <t>2,09; 5,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,58</t>
+          <t>0,9; 5,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,23</t>
+          <t>3,36; 9,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 13,01</t>
+          <t>5,97; 13,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 9,01</t>
+          <t>4,3; 7,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,54</t>
+          <t>0,95; 3,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,75</t>
+          <t>2,38; 5,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,99</t>
+          <t>3,56; 7,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,64</t>
+          <t>3,79; 6,44</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,81</t>
+          <t>0,58; 2,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,01</t>
+          <t>1,03; 4,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,51</t>
+          <t>1,62; 4,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,3</t>
+          <t>3,34; 7,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,9</t>
+          <t>3,96; 8,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 10,54</t>
+          <t>5,53; 10,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,51</t>
+          <t>4,68; 9,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,96; 13,62</t>
+          <t>8,92; 13,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,84</t>
+          <t>2,48; 4,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,69</t>
+          <t>3,82; 6,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,45</t>
+          <t>3,6; 6,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 9,72</t>
+          <t>6,69; 9,59</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,34</t>
+          <t>0,6; 3,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 8,67</t>
+          <t>4,16; 8,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,52</t>
+          <t>0,27; 2,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,44</t>
+          <t>1,12; 4,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,28</t>
+          <t>2,74; 7,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,69</t>
+          <t>8,36; 13,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,47</t>
+          <t>0,15; 1,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,31</t>
+          <t>1,05; 3,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,19</t>
+          <t>1,6; 4,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 10,24</t>
+          <t>6,97; 10,42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,1</t>
+          <t>0,45; 3,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,53</t>
+          <t>0,82; 3,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,52</t>
+          <t>3,34; 8,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,43</t>
+          <t>1,53; 5,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,39</t>
+          <t>5,06; 10,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 12,88</t>
+          <t>6,86; 13,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 10,42</t>
+          <t>6,93; 12,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,52</t>
+          <t>1,24; 3,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,48</t>
+          <t>3,33; 6,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,95</t>
+          <t>4,47; 8,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,21</t>
+          <t>5,92; 9,55</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,82</t>
+          <t>0,86; 4,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,45</t>
+          <t>0,95; 5,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,54</t>
+          <t>1,37; 7,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,17</t>
+          <t>1,77; 5,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 9,5</t>
+          <t>2,94; 9,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 23,4</t>
+          <t>12,57; 22,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 13,19</t>
+          <t>5,72; 12,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,49; 13,81</t>
+          <t>8,21; 13,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,03</t>
+          <t>2,27; 5,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 13,16</t>
+          <t>7,38; 13,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,18</t>
+          <t>4,32; 8,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,44</t>
+          <t>5,59; 8,9</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,92</t>
+          <t>0,35; 3,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,45</t>
+          <t>2,09; 7,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,8; 12,32</t>
+          <t>6,64; 12,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,15</t>
+          <t>1,07; 4,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,62</t>
+          <t>1,56; 6,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,68; 15,62</t>
+          <t>7,46; 15,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,43; 20,15</t>
+          <t>13,62; 19,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,26</t>
+          <t>0,91; 3,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,79</t>
+          <t>1,1; 3,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,23</t>
+          <t>5,48; 10,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,66; 14,89</t>
+          <t>10,77; 14,62</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,4</t>
+          <t>1,01; 3,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,52 +1567,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,01</t>
+          <t>3,39; 7,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,87</t>
+          <t>4,02; 7,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,42</t>
+          <t>2,41; 5,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,24</t>
+          <t>1,6; 4,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,8</t>
+          <t>6,42; 10,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,62; 13,34</t>
+          <t>10,54; 14,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,03</t>
+          <t>2,07; 3,92</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,93</t>
+          <t>1,25; 2,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,18</t>
+          <t>5,38; 8,37</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,84</t>
+          <t>7,78; 10,67</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,5</t>
+          <t>2,67; 5,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,85</t>
+          <t>1,84; 4,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,06</t>
+          <t>0,5; 2,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,57</t>
+          <t>2,84; 5,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,16</t>
+          <t>4,49; 8,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,92</t>
+          <t>5,93; 9,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,52</t>
+          <t>3,94; 7,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,23; 11,52</t>
+          <t>6,71; 9,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,31</t>
+          <t>3,96; 6,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,68</t>
+          <t>4,3; 6,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,41</t>
+          <t>2,51; 4,46</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,24; 7,0</t>
+          <t>5,16; 7,14</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,53</t>
+          <t>1,57; 2,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,59</t>
+          <t>1,52; 2,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,21</t>
+          <t>2,14; 3,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,75; 5,61</t>
+          <t>4,49; 5,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,88</t>
+          <t>3,51; 4,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,09</t>
+          <t>5,54; 7,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,62; 8,5</t>
+          <t>6,7; 8,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,96; 10,91</t>
+          <t>9,58; 11,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,65; 3,51</t>
+          <t>2,71; 3,52</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,79; 4,76</t>
+          <t>3,75; 4,76</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,62; 5,72</t>
+          <t>4,62; 5,7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,16</t>
+          <t>7,29; 8,41</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>31311</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>982; 11790</t>
+          <t>873; 10406</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2711; 14182</t>
+          <t>2674; 14059</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2641; 15145</t>
+          <t>2796; 14959</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5903; 18360</t>
+          <t>6659; 18865</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2741; 14565</t>
+          <t>2358; 14084</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9505; 25784</t>
+          <t>9375; 26977</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16082; 37547</t>
+          <t>17229; 38487</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14001; 26088</t>
+          <t>13604; 25175</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5451; 18876</t>
+          <t>5090; 19772</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13845; 32823</t>
+          <t>13593; 32605</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22866; 46546</t>
+          <t>20754; 46494</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22965; 39920</t>
+          <t>24044; 40898</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25386</t>
+          <t>27250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57855</t>
+          <t>59807</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83241</t>
+          <t>87057</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2870; 13834</t>
+          <t>2848; 13604</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6005; 25329</t>
+          <t>5208; 23980</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7203; 22654</t>
+          <t>8149; 22815</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16478; 37781</t>
+          <t>17706; 41145</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19151; 39817</t>
+          <t>19943; 40351</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29072; 55077</t>
+          <t>28922; 55419</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25637; 49754</t>
+          <t>24493; 49263</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46046; 69955</t>
+          <t>48651; 72565</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26930; 48299</t>
+          <t>24721; 47888</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37662; 68779</t>
+          <t>39249; 70193</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37796; 66175</t>
+          <t>36910; 64899</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68646; 100201</t>
+          <t>71961; 103043</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>19798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37714</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56330</t>
+          <t>58128</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5225</t>
+          <t>0; 4364</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1931; 10789</t>
+          <t>1945; 11112</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 8146</t>
+          <t>0; 7357</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12424; 27365</t>
+          <t>13124; 27358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>911; 8441</t>
+          <t>914; 8681</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3984; 15148</t>
+          <t>3817; 15612</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9098; 24482</t>
+          <t>9202; 24703</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29562; 47790</t>
+          <t>29779; 48009</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>974; 9615</t>
+          <t>992; 9946</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7150; 21986</t>
+          <t>6993; 22902</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10806; 27466</t>
+          <t>10462; 27309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>45658; 68059</t>
+          <t>46830; 70012</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35125</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54520</t>
+          <t>58945</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1003; 11111</t>
+          <t>1620; 12000</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3042; 13206</t>
+          <t>3049; 14129</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4504; 15743</t>
+          <t>4517; 15743</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11615; 29749</t>
+          <t>12448; 32670</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5880; 20183</t>
+          <t>5699; 19459</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19712; 40300</t>
+          <t>19644; 39492</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26361; 49877</t>
+          <t>26574; 50340</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20465; 49517</t>
+          <t>29213; 51960</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8880; 25668</t>
+          <t>9080; 26279</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25820; 49404</t>
+          <t>25394; 48733</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32646; 60203</t>
+          <t>33816; 60598</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37922; 72602</t>
+          <t>47078; 75869</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22465</t>
+          <t>23738</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>30596</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1722; 9801</t>
+          <t>1756; 10024</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1973; 11595</t>
+          <t>2028; 11698</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2915; 15918</t>
+          <t>2890; 14888</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3577; 11026</t>
+          <t>3650; 11870</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6251; 19737</t>
+          <t>6113; 19894</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28040; 51390</t>
+          <t>27612; 49953</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11480; 28821</t>
+          <t>12500; 28067</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17719; 28814</t>
+          <t>18661; 29955</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9116; 24777</t>
+          <t>9347; 24588</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31363; 56867</t>
+          <t>31896; 57415</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17702; 39441</t>
+          <t>18554; 38420</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22862; 36589</t>
+          <t>24195; 38538</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24764</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>42381</t>
+          <t>43483</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>67144</t>
+          <t>67836</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>953; 7898</t>
+          <t>951; 8662</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6276</t>
+          <t>0; 7772</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5389; 16977</t>
+          <t>5493; 18646</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18335; 33212</t>
+          <t>17968; 32551</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3027; 14316</t>
+          <t>2977; 13586</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4886; 18484</t>
+          <t>4356; 18557</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20964; 42664</t>
+          <t>20361; 41692</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34519; 51801</t>
+          <t>35934; 52334</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4870; 17879</t>
+          <t>5009; 17837</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6170; 20963</t>
+          <t>6094; 20832</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28744; 54852</t>
+          <t>29367; 55160</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>56147; 78418</t>
+          <t>57587; 78143</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34763</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>81358</t>
+          <t>96443</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>116121</t>
+          <t>136327</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7259; 20909</t>
+          <t>6235; 19926</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3064; 16262</t>
+          <t>3033; 16290</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23028; 45995</t>
+          <t>22245; 46383</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23295; 49157</t>
+          <t>28900; 56282</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15544; 34586</t>
+          <t>15410; 36071</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11333; 29425</t>
+          <t>11084; 29345</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44022; 74661</t>
+          <t>44374; 74984</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>39211; 113283</t>
+          <t>81243; 112455</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25813; 50553</t>
+          <t>25955; 49145</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16940; 39689</t>
+          <t>16892; 38680</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72922; 110214</t>
+          <t>72550; 112813</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>75264; 144968</t>
+          <t>115976; 159029</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27616</t>
+          <t>31091</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>63452</t>
+          <t>67710</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91068</t>
+          <t>98801</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20061; 40818</t>
+          <t>19851; 40641</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15616; 37633</t>
+          <t>14246; 35808</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3836; 16056</t>
+          <t>3886; 16862</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11698; 42398</t>
+          <t>22680; 42373</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>35489; 63909</t>
+          <t>35189; 62810</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>48119; 81532</t>
+          <t>48753; 80116</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>32999; 62144</t>
+          <t>32543; 62252</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>51710; 82357</t>
+          <t>55700; 80554</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>62016; 96306</t>
+          <t>60510; 95329</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>68625; 106696</t>
+          <t>68625; 107487</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>39766; 70804</t>
+          <t>40307; 71626</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>53307; 115117</t>
+          <t>84032; 116195</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>167783</t>
+          <t>181771</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>359919</t>
+          <t>387229</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>527702</t>
+          <t>569001</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>50187; 82874</t>
+          <t>51342; 83533</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>54220; 88623</t>
+          <t>51830; 89358</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71362; 109099</t>
+          <t>72586; 113046</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>129731; 193911</t>
+          <t>158617; 210388</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>118361; 165057</t>
+          <t>118772; 165490</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>196652; 251511</t>
+          <t>196237; 252201</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>234505; 301382</t>
+          <t>237364; 302058</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>291033; 399005</t>
+          <t>357335; 418483</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>176275; 233535</t>
+          <t>180315; 234048</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>263880; 331559</t>
+          <t>260782; 331267</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>320372; 396633</t>
+          <t>320580; 395757</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>459592; 580537</t>
+          <t>529545; 610851</t>
         </is>
       </c>
     </row>
